--- a/Stats Sheet/Round Gaps/Absorbed.xlsx
+++ b/Stats Sheet/Round Gaps/Absorbed.xlsx
@@ -346,7 +346,7 @@
     <x:t>Trenzey</x:t>
   </x:si>
   <x:si>
-    <x:t>Yist</x:t>
+    <x:t>yistv2</x:t>
   </x:si>
   <x:si>
     <x:t>AeroCash</x:t>
